--- a/2313.HK.xlsx
+++ b/2313.HK.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE29B762-A7CA-41AA-8E18-8BA536B8B6F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC74FBF-D1AF-4428-9F6A-26D23614C26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{018E0477-05D3-47A6-BBAA-907DACD6F8C2}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{018E0477-05D3-47A6-BBAA-907DACD6F8C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
-    <sheet name="Financials" sheetId="2" r:id="rId2"/>
+    <sheet name="Model" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
   <si>
     <t>Shenzou International</t>
   </si>
@@ -72,9 +72,6 @@
     <t>H224</t>
   </si>
   <si>
-    <t>Price</t>
-  </si>
-  <si>
     <t>Shares</t>
   </si>
   <si>
@@ -85,9 +82,6 @@
   </si>
   <si>
     <t>Debt</t>
-  </si>
-  <si>
-    <t>Q224</t>
   </si>
   <si>
     <t>EV</t>
@@ -146,18 +140,108 @@
   <si>
     <t>EPS</t>
   </si>
+  <si>
+    <t>Price RMB</t>
+  </si>
+  <si>
+    <t>Price HKD</t>
+  </si>
+  <si>
+    <t>HKD/RMB</t>
+  </si>
+  <si>
+    <t>H125</t>
+  </si>
+  <si>
+    <t>H225</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>4 Big Costumers:</t>
+  </si>
+  <si>
+    <t>Costumer A</t>
+  </si>
+  <si>
+    <t>Costumer B</t>
+  </si>
+  <si>
+    <t>Costumer C</t>
+  </si>
+  <si>
+    <t>Costumer D</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>% of Rev</t>
+  </si>
+  <si>
+    <t>Uniqlo</t>
+  </si>
+  <si>
+    <t>Nike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adidas </t>
+  </si>
+  <si>
+    <t>Puma</t>
+  </si>
+  <si>
+    <t>Guess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produce Apparel and knit components </t>
+  </si>
+  <si>
+    <t>Workforce</t>
+  </si>
+  <si>
+    <t>Revenue Growth</t>
+  </si>
+  <si>
+    <t>Gross Margin</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>Tax Rate</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -187,6 +271,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -205,28 +304,40 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -558,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64355586-6FF6-4399-B76F-E69240B75FAF}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="2" customWidth="1"/>
@@ -574,78 +685,198 @@
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="2">
+        <v>47.12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="10">
+        <f>+J2*J10</f>
+        <v>41.465599999999995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="2">
-        <v>58.65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="I3" s="2" t="s">
+      <c r="J4" s="3">
+        <v>1503.222397</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="3">
-        <v>1503.222397</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="J5" s="3">
+        <f>+J3*J4</f>
+        <v>62332.018625043194</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="3">
-        <f>+J2*J3</f>
-        <v>88163.993584049997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="3">
-        <f>10081.734+9236.322</f>
-        <v>19318.056</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="I6" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="J6" s="3">
-        <f>9027.793+1800</f>
-        <v>10827.793</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>16</v>
+        <f>15117.148+10320.273</f>
+        <v>25437.420999999998</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J7" s="3">
-        <f>+J4-J5+J6</f>
-        <v>79673.730584050005</v>
+        <v>14701.28</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="3">
+        <f>+J5-J6+J7</f>
+        <v>51595.877625043198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B9" s="12" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H10" s="3"/>
+      <c r="B10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B11" s="9"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="3">
+        <v>101720</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="8">
+        <v>4333.0709999999999</v>
+      </c>
+      <c r="E15" s="14">
+        <f>+D15/Model!$I$7</f>
+        <v>0.28952023414607025</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="8">
+        <v>3435.558</v>
+      </c>
+      <c r="E16" s="14">
+        <f>+D16/Model!$I$7</f>
+        <v>0.22955164052987015</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B17" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="8">
+        <v>2992.45</v>
+      </c>
+      <c r="E17" s="14">
+        <f>+D17/Model!$I$7</f>
+        <v>0.19994475619494995</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B18" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="8">
+        <v>1532.2090000000001</v>
+      </c>
+      <c r="E18" s="14">
+        <f>+D18/Model!$I$7</f>
+        <v>0.10237669967575334</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B19" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="13">
+        <f>+SUM(D15:D18)</f>
+        <v>12293.288</v>
+      </c>
+      <c r="E19" s="14">
+        <f>+D19/Model!$I$7</f>
+        <v>0.82139333054664376</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" xr:uid="{5E987129-716B-43D3-B1A1-37FFB3CF711C}"/>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{5E987129-716B-43D3-B1A1-37FFB3CF711C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -685,11 +916,17 @@
       <c r="H2" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="I2" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -701,7 +938,9 @@
         <v>9212.5460000000003</v>
       </c>
       <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="I3" s="3">
+        <v>10128.585999999999</v>
+      </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -726,7 +965,7 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -738,7 +977,9 @@
         <v>2760.739</v>
       </c>
       <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="I4" s="3">
+        <v>3792.1329999999998</v>
+      </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -763,7 +1004,7 @@
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -775,7 +1016,9 @@
         <v>903.18200000000002</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="I5" s="3">
+        <v>940.21100000000001</v>
+      </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -800,7 +1043,7 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -812,7 +1055,9 @@
         <v>99.504000000000005</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="I6" s="3">
+        <v>105.45399999999999</v>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -837,7 +1082,7 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="7">
         <f t="shared" ref="C7:F7" si="0">+SUM(C3:C6)</f>
@@ -863,8 +1108,10 @@
         <f t="shared" ref="H7" si="1">+SUM(H3:H6)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="I7" s="7">
+        <v>14966.384</v>
+      </c>
+      <c r="J7" s="7"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -888,7 +1135,7 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -900,7 +1147,9 @@
         <v>9214.5020000000004</v>
       </c>
       <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="I8" s="3">
+        <v>10908.366</v>
+      </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -925,7 +1174,7 @@
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" ref="C9:F9" si="2">+C7-C8</f>
@@ -948,10 +1197,13 @@
         <v>3761.469000000001</v>
       </c>
       <c r="H9" s="3">
-        <f t="shared" ref="H9" si="3">+H7-H8</f>
+        <f t="shared" ref="H9:I9" si="3">+H7-H8</f>
         <v>0</v>
       </c>
-      <c r="I9" s="3"/>
+      <c r="I9" s="3">
+        <f t="shared" si="3"/>
+        <v>4058.018</v>
+      </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -976,7 +1228,7 @@
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -988,7 +1240,9 @@
         <v>635.46299999999997</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="I10" s="3">
+        <v>799.39700000000005</v>
+      </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -1013,7 +1267,7 @@
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -1025,7 +1279,9 @@
         <v>84.837000000000003</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="I11" s="3">
+        <v>108.75700000000001</v>
+      </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -1050,7 +1306,7 @@
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -1062,7 +1318,9 @@
         <v>943.697</v>
       </c>
       <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="I12" s="3">
+        <v>1081.8</v>
+      </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -1087,7 +1345,7 @@
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" ref="C13:F13" si="4">+C9+C10-SUM(C11:C12)</f>
@@ -1110,10 +1368,13 @@
         <v>3368.3980000000006</v>
       </c>
       <c r="H13" s="3">
-        <f t="shared" ref="H13" si="5">+H9+H10-SUM(H11:H12)</f>
+        <f t="shared" ref="H13:I13" si="5">+H9+H10-SUM(H11:H12)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="3"/>
+      <c r="I13" s="3">
+        <f t="shared" si="5"/>
+        <v>3666.8580000000002</v>
+      </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -1138,7 +1399,7 @@
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -1150,7 +1411,9 @@
         <v>191.38900000000001</v>
       </c>
       <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="I14" s="3">
+        <v>175.886</v>
+      </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -1175,7 +1438,7 @@
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -1187,7 +1450,9 @@
         <v>69.64</v>
       </c>
       <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="I15" s="3">
+        <v>139.196</v>
+      </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -1212,7 +1477,7 @@
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -1224,7 +1489,9 @@
         <v>2.56</v>
       </c>
       <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="I16" s="3">
+        <v>1.952</v>
+      </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -1249,7 +1516,7 @@
     </row>
     <row r="17" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" ref="C17:F17" si="6">+C13-C14+C15+C16</f>
@@ -1272,10 +1539,13 @@
         <v>3249.2090000000003</v>
       </c>
       <c r="H17" s="3">
-        <f t="shared" ref="H17" si="7">+H13-H14+H15+H16</f>
+        <f t="shared" ref="H17:I17" si="7">+H13-H14+H15+H16</f>
         <v>0</v>
       </c>
-      <c r="I17" s="3"/>
+      <c r="I17" s="3">
+        <f t="shared" si="7"/>
+        <v>3632.1200000000003</v>
+      </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
@@ -1300,7 +1570,7 @@
     </row>
     <row r="18" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -1312,7 +1582,9 @@
         <v>318.18099999999998</v>
       </c>
       <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="I18" s="3">
+        <v>455.28399999999999</v>
+      </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
@@ -1337,7 +1609,7 @@
     </row>
     <row r="19" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" ref="C19:F19" si="8">+C17-C18</f>
@@ -1360,10 +1632,13 @@
         <v>2931.0280000000002</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" ref="H19" si="9">+H17-H18</f>
+        <f t="shared" ref="H19:I19" si="9">+H17-H18</f>
         <v>0</v>
       </c>
-      <c r="I19" s="3"/>
+      <c r="I19" s="3">
+        <f t="shared" si="9"/>
+        <v>3176.8360000000002</v>
+      </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
@@ -1418,7 +1693,7 @@
     </row>
     <row r="21" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C21" s="8" t="e">
         <f t="shared" ref="C21:D21" si="10">+C19/C22</f>
@@ -1433,7 +1708,7 @@
         <v>1.4148465351797168</v>
       </c>
       <c r="F21" s="8" t="e">
-        <f t="shared" ref="F21:H21" si="11">+F19/F22</f>
+        <f t="shared" ref="F21:I21" si="11">+F19/F22</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G21" s="8">
@@ -1444,7 +1719,10 @@
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I21" s="3"/>
+      <c r="I21" s="8">
+        <f t="shared" si="11"/>
+        <v>2.1133506301795744</v>
+      </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
@@ -1469,7 +1747,7 @@
     </row>
     <row r="22" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -1481,7 +1759,9 @@
         <v>1503.222397</v>
       </c>
       <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="I22" s="3">
+        <v>1503.222397</v>
+      </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
@@ -1565,13 +1845,31 @@
       <c r="AD24" s="3"/>
     </row>
     <row r="25" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B25" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+      <c r="E25" s="16" t="e">
+        <f>+E7/C7-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F25" s="16" t="e">
+        <f>+F7/D7-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G25" s="16">
+        <f>+G7/E7-1</f>
+        <v>0.12229836077994394</v>
+      </c>
+      <c r="H25" s="16" t="e">
+        <f>+H7/F7-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I25" s="16">
+        <f>+I7/G7-1</f>
+        <v>0.15339222012749554</v>
+      </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
@@ -1595,13 +1893,31 @@
       <c r="AD25" s="3"/>
     </row>
     <row r="26" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B26" s="15" t="s">
+        <v>56</v>
+      </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="E26" s="14">
+        <f>+E9/E7</f>
+        <v>0.22443457260973515</v>
+      </c>
+      <c r="F26" s="14" t="e">
+        <f>+F9/F7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G26" s="14">
+        <f>+G9/G7</f>
+        <v>0.28987957818339766</v>
+      </c>
+      <c r="H26" s="14" t="e">
+        <f>+H9/H7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I26" s="14">
+        <f>+I9/I7</f>
+        <v>0.27114218103718307</v>
+      </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
@@ -1625,13 +1941,31 @@
       <c r="AD26" s="3"/>
     </row>
     <row r="27" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B27" s="15" t="s">
+        <v>57</v>
+      </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="E27" s="14">
+        <f>+E13/E7</f>
+        <v>0.182276156935994</v>
+      </c>
+      <c r="F27" s="14" t="e">
+        <f>+F13/F7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G27" s="14">
+        <f>+G13/G7</f>
+        <v>0.25958735573622971</v>
+      </c>
+      <c r="H27" s="14" t="e">
+        <f>+H13/H7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I27" s="14">
+        <f>+I13/I7</f>
+        <v>0.24500627539691619</v>
+      </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
@@ -1655,13 +1989,31 @@
       <c r="AD27" s="3"/>
     </row>
     <row r="28" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B28" s="15" t="s">
+        <v>58</v>
+      </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+      <c r="E28" s="14">
+        <f>+E18/E17</f>
+        <v>9.4359025457072546E-2</v>
+      </c>
+      <c r="F28" s="14" t="e">
+        <f>+F18/F17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G28" s="14">
+        <f>+G18/G17</f>
+        <v>9.7925679757750253E-2</v>
+      </c>
+      <c r="H28" s="14" t="e">
+        <f>+H18/H17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I28" s="14">
+        <f>+I18/I17</f>
+        <v>0.12534938272964549</v>
+      </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>

--- a/2313.HK.xlsx
+++ b/2313.HK.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC74FBF-D1AF-4428-9F6A-26D23614C26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5BE72B-E2A8-4537-A7C9-244C0081CC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{018E0477-05D3-47A6-BBAA-907DACD6F8C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{018E0477-05D3-47A6-BBAA-907DACD6F8C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>Shenzou International</t>
   </si>
@@ -198,9 +198,6 @@
     <t>Guess</t>
   </si>
   <si>
-    <t xml:space="preserve">Produce Apparel and knit components </t>
-  </si>
-  <si>
     <t>Workforce</t>
   </si>
   <si>
@@ -215,6 +212,15 @@
   <si>
     <t>Tax Rate</t>
   </si>
+  <si>
+    <t xml:space="preserve">Produce Apparel and knit wear </t>
+  </si>
+  <si>
+    <t>produce finished products based on designs by costumers</t>
+  </si>
+  <si>
+    <t>and specialized components e.g. for Nike</t>
+  </si>
 </sst>
 </file>
 
@@ -223,13 +229,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -306,33 +318,34 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -765,8 +778,8 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B10" s="15" t="s">
-        <v>53</v>
+      <c r="B10" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>36</v>
@@ -776,12 +789,17 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B11" s="9"/>
+      <c r="B11" s="17" t="s">
+        <v>59</v>
+      </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B12" s="17" t="s">
+        <v>60</v>
+      </c>
       <c r="I12" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J12" s="3">
         <v>101720</v>
@@ -1846,7 +1864,7 @@
     </row>
     <row r="25" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -1894,7 +1912,7 @@
     </row>
     <row r="26" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B26" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -1942,7 +1960,7 @@
     </row>
     <row r="27" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B27" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -1990,7 +2008,7 @@
     </row>
     <row r="28" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B28" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
